--- a/data/trans_bre/P1428-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1428-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,85</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>162,23%</t>
+          <t>170,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,9</t>
+          <t>15,81; 22,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 16,23</t>
+          <t>9,67; 16,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 16,54</t>
+          <t>9,57; 16,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 24,71</t>
+          <t>17,06; 24,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,42; 161,92</t>
+          <t>94,23; 164,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,54; 161,82</t>
+          <t>74,12; 166,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97; 253,73</t>
+          <t>96,52; 241,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>113,21; 231,01</t>
+          <t>118,02; 230,37</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,68</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>340,9%</t>
+          <t>121,44%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,76</t>
+          <t>1,52; 4,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,65</t>
+          <t>1,03; 3,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,09</t>
+          <t>1,78; 4,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 35,61</t>
+          <t>4,03; 6,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,59; 155,63</t>
+          <t>36,95; 159,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,81; 166,54</t>
+          <t>26,93; 173,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,63; 209,94</t>
+          <t>59,48; 221,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>105,83; 978,38</t>
+          <t>79,86; 176,32</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>196,52%</t>
+          <t>199,14%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,35</t>
+          <t>0,63; 5,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,72</t>
+          <t>-0,3; 5,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,43</t>
+          <t>-0,85; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,87</t>
+          <t>3,23; 7,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 370,45</t>
+          <t>13,38; 368,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 484,88</t>
+          <t>-12,55; 395,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 393,27</t>
+          <t>-36,39; 468,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73,47; 382,86</t>
+          <t>85,12; 391,37</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,09</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>279,58%</t>
+          <t>172,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,96</t>
+          <t>8,87; 12,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,57</t>
+          <t>5,75; 8,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,95</t>
+          <t>4,49; 7,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 28,32</t>
+          <t>7,95; 10,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>114,3; 185,56</t>
+          <t>112,27; 182,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>103,75; 189,33</t>
+          <t>99,53; 186,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>112,45; 223,29</t>
+          <t>112,16; 228,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>166,29; 693,28</t>
+          <t>133,97; 214,23</t>
         </is>
       </c>
     </row>
